--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260819.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260819.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.97%</t>
+          <t>9.74%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>177,211,000</t>
+          <t>177,011,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.51%</t>
+          <t>9.63%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>5.98%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.90%</t>
         </is>
       </c>
     </row>
@@ -704,95 +704,95 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.31%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>187,201,000</t>
+          <t>602,716,270</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.60%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>602,716,270</t>
+          <t>187,201,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.55%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,062,000</t>
+          <t>27,239,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>27,239,000</t>
+          <t>5,062,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>64,392,000</t>
+          <t>64,092,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
@@ -902,205 +902,205 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>26,219,000</t>
+          <t>199,761,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>98,298,442</t>
+          <t>26,219,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>199,761,000</t>
+          <t>83,020,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>236,458,056</t>
+          <t>98,298,442</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>83,020,000</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>145,204,000</t>
+          <t>236,458,056</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>131,081,000</t>
+          <t>145,204,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>28,901,000</t>
+          <t>99,033,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>99,033,000</t>
+          <t>28,901,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>54,488,000</t>
+          <t>1,364</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,274</t>
+          <t>54,488,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -1232,51 +1232,51 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,761,000</t>
+          <t>91,230,061</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>91,230,061</t>
+          <t>13,241,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>26,084,565,032</t>
+          <t>26,442,630,565</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,790,098,402</t>
+          <t>4,616,516,894</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-459,541,339</t>
+          <t>-11,451,545</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
